--- a/VT_REG1_RCA_V12.xlsx
+++ b/VT_REG1_RCA_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261017\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0A16FB-5AEE-4ED0-B261-610F28DE3123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2AA01D-8635-46A9-B337-09370576D06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -33,6 +33,19 @@
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -9282,26 +9295,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA33"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="10.88671875" customWidth="1"/>
-    <col min="13" max="13" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="10.88671875" customWidth="1"/>
-    <col min="22" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.85546875" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
       <c r="X1" s="20" t="s">
         <v>92</v>
       </c>
@@ -9315,7 +9328,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:27" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D2" s="35" t="s">
         <v>44</v>
       </c>
@@ -9383,7 +9396,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="2:27" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.2">
       <c r="C3" s="59" t="s">
         <v>125</v>
       </c>
@@ -9445,7 +9458,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B4" s="33"/>
       <c r="C4" s="76" t="s">
         <v>57</v>
@@ -9469,7 +9482,7 @@
       <c r="U4" s="5"/>
       <c r="V4" s="77"/>
     </row>
-    <row r="5" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B5" s="37" t="s">
         <v>58</v>
       </c>
@@ -9553,7 +9566,7 @@
         <v>53.616579479999999</v>
       </c>
     </row>
-    <row r="6" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B6" s="37" t="s">
         <v>60</v>
       </c>
@@ -9637,7 +9650,7 @@
         <v>17.352778751999999</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B7" s="37" t="s">
         <v>62</v>
       </c>
@@ -9721,7 +9734,7 @@
         <v>105.16278636</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B8" s="37" t="s">
         <v>64</v>
       </c>
@@ -9805,7 +9818,7 @@
         <v>8.9932882680000006</v>
       </c>
     </row>
-    <row r="9" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B9" s="37" t="s">
         <v>66</v>
       </c>
@@ -9889,7 +9902,7 @@
         <v>101.39634108000001</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B10" s="37" t="s">
         <v>68</v>
       </c>
@@ -9973,7 +9986,7 @@
         <v>9.4588185599999992</v>
       </c>
     </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B11" s="37" t="s">
         <v>85</v>
       </c>
@@ -10057,7 +10070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B12" s="37" t="s">
         <v>86</v>
       </c>
@@ -10141,7 +10154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="75" t="s">
         <v>88</v>
       </c>
@@ -10225,7 +10238,7 @@
         <v>295.9805925</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
@@ -10236,7 +10249,7 @@
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
       <c r="D15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
@@ -10247,7 +10260,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="2:27" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
       <c r="C16" s="42" t="s">
         <v>147</v>
       </c>
@@ -10262,7 +10275,7 @@
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D17" s="6"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
@@ -10273,7 +10286,7 @@
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
       <c r="D18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
@@ -10284,7 +10297,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
     </row>
-    <row r="19" spans="2:24" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B19" s="22" t="s">
         <v>100</v>
       </c>
@@ -10349,7 +10362,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B20" s="37" t="s">
         <v>64</v>
       </c>
@@ -10380,7 +10393,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="82" t="s">
         <v>58</v>
       </c>
@@ -10417,7 +10430,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B22" s="82" t="s">
         <v>58</v>
       </c>
@@ -10450,7 +10463,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B23" s="82" t="s">
         <v>58</v>
       </c>
@@ -10490,7 +10503,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="82" t="s">
         <v>60</v>
       </c>
@@ -10525,7 +10538,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="82" t="s">
         <v>60</v>
       </c>
@@ -10558,7 +10571,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
       <c r="B26" s="82" t="s">
         <v>60</v>
       </c>
@@ -10598,7 +10611,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C29" s="55" t="s">
         <v>107</v>
       </c>
@@ -10609,7 +10622,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
         <v>117</v>
       </c>
@@ -10623,7 +10636,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B31" s="37" t="s">
         <v>64</v>
       </c>
@@ -10633,7 +10646,7 @@
       <c r="D31" s="87"/>
       <c r="E31" s="88"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B32" s="37" t="s">
         <v>58</v>
       </c>
@@ -10643,7 +10656,7 @@
       <c r="D32" s="53"/>
       <c r="E32" s="90"/>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B33" s="37" t="s">
         <v>60</v>
       </c>
@@ -10662,20 +10675,20 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B3:R24"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" customWidth="1"/>
-    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" customWidth="1"/>
+    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="29" t="s">
         <v>155</v>
       </c>
@@ -10692,7 +10705,7 @@
       <c r="M3" s="29"/>
       <c r="N3" s="29"/>
     </row>
-    <row r="4" spans="2:18" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
       <c r="D4" s="30"/>
@@ -10701,7 +10714,7 @@
       <c r="G4" s="30"/>
       <c r="H4" s="30"/>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B5" s="28" t="s">
         <v>142</v>
       </c>
@@ -10712,7 +10725,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="31" t="s">
         <v>0</v>
       </c>
@@ -10769,7 +10782,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>90</v>
       </c>
@@ -10817,7 +10830,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B8">
         <f>DemTechs_AGR!$Q8</f>
         <v>0</v>
@@ -10868,13 +10881,13 @@
         <v>112</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B23" s="39"/>
       <c r="C23" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B24" s="61"/>
       <c r="C24" s="1" t="s">
         <v>150</v>
@@ -10889,20 +10902,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J5"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.88671875" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" customWidth="1"/>
-    <col min="3" max="3" width="6.88671875" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" customWidth="1"/>
+    <col min="1" max="1" width="1.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="18" x14ac:dyDescent="0.25">
       <c r="B3" s="67" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="E5" s="68" t="s">
         <v>158</v>
       </c>
@@ -10922,29 +10935,29 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R41"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -10965,7 +10978,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -11001,7 +11014,7 @@
       <c r="Q2" s="120"/>
       <c r="R2" s="120"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="121" t="s">
         <v>7</v>
       </c>
@@ -11030,7 +11043,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11064,7 +11077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="154"/>
       <c r="F5" s="154"/>
       <c r="G5" s="155"/>
@@ -11090,7 +11103,7 @@
       <c r="Q5" s="124"/>
       <c r="R5" s="124"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="154"/>
       <c r="F6" s="154"/>
       <c r="G6" s="155"/>
@@ -11114,7 +11127,7 @@
       <c r="Q6" s="124"/>
       <c r="R6" s="124"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="154"/>
       <c r="F7" s="154"/>
       <c r="G7" s="155"/>
@@ -11138,7 +11151,7 @@
       <c r="Q7" s="124"/>
       <c r="R7" s="124"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="154"/>
       <c r="F8" s="154"/>
       <c r="G8" s="155"/>
@@ -11162,7 +11175,7 @@
       <c r="Q8" s="124"/>
       <c r="R8" s="124"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="154"/>
       <c r="F9" s="154"/>
       <c r="G9" s="155"/>
@@ -11190,18 +11203,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="154"/>
       <c r="F10" s="154"/>
       <c r="G10" s="155"/>
       <c r="H10" s="156"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
@@ -11219,7 +11232,7 @@
       <c r="Q12" s="124"/>
       <c r="R12" s="124"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -11269,7 +11282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
@@ -11319,7 +11332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>90</v>
       </c>
@@ -11346,7 +11359,7 @@
       <c r="Q15" s="126"/>
       <c r="R15" s="126"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f>L16</f>
         <v>FTE-AGRCOA</v>
@@ -11390,7 +11403,7 @@
       <c r="Q16" s="124"/>
       <c r="R16" s="124"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-AGRGAS</v>
@@ -11432,7 +11445,7 @@
       <c r="Q17" s="124"/>
       <c r="R17" s="124"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-AGROIL</v>
@@ -11474,7 +11487,7 @@
       <c r="Q18" s="124"/>
       <c r="R18" s="124"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
         <f>[3]EB2!$H$2</f>
         <v>KER</v>
@@ -11504,7 +11517,7 @@
       <c r="Q19" s="124"/>
       <c r="R19" s="124"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
         <f>[3]EB2!$I$2</f>
         <v>LPG</v>
@@ -11536,7 +11549,7 @@
       <c r="Q20" s="124"/>
       <c r="R20" s="124"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
         <f>[3]EB2!$J$2</f>
         <v>GSL</v>
@@ -11546,7 +11559,7 @@
       <c r="H21" s="156"/>
       <c r="M21" s="19"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
         <f>[3]EB2!$L$2</f>
         <v>HFO</v>
@@ -11556,7 +11569,7 @@
       <c r="H22" s="156"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
         <f>[3]EB2!$M$2</f>
         <v>OPP</v>
@@ -11566,7 +11579,7 @@
       <c r="H23" s="156"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" t="str">
         <f>L19</f>
         <v>FTE-AGRBIO</v>
@@ -11590,7 +11603,7 @@
       <c r="K24" s="23"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-AGRELC</v>
@@ -11614,7 +11627,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="66"/>
@@ -11623,20 +11636,20 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="66"/>
       <c r="H27" s="10"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="11"/>
@@ -11644,7 +11657,7 @@
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="11"/>
@@ -11652,7 +11665,7 @@
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="95"/>
@@ -11660,7 +11673,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="95"/>
@@ -11668,7 +11681,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -11676,7 +11689,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -11684,7 +11697,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="11"/>
@@ -11692,7 +11705,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="11"/>
@@ -11700,13 +11713,13 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="39"/>
       <c r="C40" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="61"/>
       <c r="C41" s="1" t="s">
         <v>150</v>
@@ -11723,34 +11736,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:W31"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="5.5546875" customWidth="1"/>
-    <col min="13" max="13" width="8.109375" customWidth="1"/>
-    <col min="14" max="14" width="8.88671875" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="57.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" customWidth="1"/>
-    <col min="20" max="20" width="11.6640625" customWidth="1"/>
-    <col min="21" max="21" width="13.44140625" customWidth="1"/>
-    <col min="22" max="22" width="13.88671875" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="57.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.28515625" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" customWidth="1"/>
+    <col min="22" max="22" width="13.85546875" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -11776,7 +11789,7 @@
       </c>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="2:23" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B8</f>
         <v>AGR</v>
@@ -11818,7 +11831,7 @@
       <c r="V2" s="120"/>
       <c r="W2" s="120"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
       <c r="M3" s="121" t="s">
         <v>7</v>
       </c>
@@ -11843,7 +11856,7 @@
       <c r="V3" s="120"/>
       <c r="W3" s="120"/>
     </row>
-    <row r="4" spans="2:23" ht="42.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:23" ht="46.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -11874,7 +11887,7 @@
       <c r="V4" s="120"/>
       <c r="W4" s="120"/>
     </row>
-    <row r="5" spans="2:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -11904,7 +11917,7 @@
       <c r="V5" s="120"/>
       <c r="W5" s="120"/>
     </row>
-    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.2">
       <c r="M6" s="124" t="s">
         <v>106</v>
       </c>
@@ -11928,7 +11941,7 @@
       <c r="V6" s="120"/>
       <c r="W6" s="120"/>
     </row>
-    <row r="7" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="G7" s="159" t="s">
         <v>180</v>
       </c>
@@ -11938,7 +11951,7 @@
       <c r="V7" s="120"/>
       <c r="W7" s="120"/>
     </row>
-    <row r="8" spans="2:23" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:23" ht="15" x14ac:dyDescent="0.25">
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
@@ -11964,7 +11977,7 @@
       <c r="V8" s="120"/>
       <c r="W8" s="124"/>
     </row>
-    <row r="9" spans="2:23" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:23" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B9" s="17" t="s">
         <v>1</v>
       </c>
@@ -12018,7 +12031,7 @@
       <c r="U9" s="120"/>
       <c r="V9" s="120"/>
     </row>
-    <row r="10" spans="2:23" ht="42" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:23" ht="45.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="15" t="s">
         <v>39</v>
       </c>
@@ -12073,7 +12086,7 @@
       <c r="V10" s="120"/>
       <c r="W10" s="124"/>
     </row>
-    <row r="11" spans="2:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>90</v>
       </c>
@@ -12104,7 +12117,7 @@
       <c r="V11" s="120"/>
       <c r="W11" s="124"/>
     </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B12" t="str">
         <f>O12</f>
         <v>AOTETOT</v>
@@ -12161,7 +12174,7 @@
       <c r="V12" s="120"/>
       <c r="W12" s="124"/>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>183</v>
       </c>
@@ -12197,7 +12210,7 @@
       <c r="V13" s="120"/>
       <c r="W13" s="124"/>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>183</v>
       </c>
@@ -12234,7 +12247,7 @@
       <c r="V14" s="124"/>
       <c r="W14" s="124"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>183</v>
       </c>
@@ -12268,7 +12281,7 @@
       <c r="V15" s="124"/>
       <c r="W15" s="124"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>183</v>
       </c>
@@ -12302,58 +12315,58 @@
       <c r="V16" s="124"/>
       <c r="W16" s="124"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J17" s="16"/>
       <c r="K17" s="16"/>
       <c r="L17" s="16"/>
       <c r="R17" s="19"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J18" s="16"/>
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
       <c r="R18" s="19"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F19" s="95"/>
       <c r="G19" s="95"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F20" s="110"/>
       <c r="G20" s="110"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="39"/>
       <c r="C26" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" s="61"/>
       <c r="C27" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F28" s="11"/>
       <c r="G28" s="11"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="F30" s="11"/>
       <c r="G30" s="11"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="N31" s="1"/>
     </row>
   </sheetData>
@@ -12368,29 +12381,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:R42"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -12411,7 +12424,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -12447,7 +12460,7 @@
       <c r="Q2" s="120"/>
       <c r="R2" s="120"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="121" t="s">
         <v>7</v>
       </c>
@@ -12476,7 +12489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -12510,7 +12523,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -12536,7 +12549,7 @@
       <c r="Q5" s="124"/>
       <c r="R5" s="124"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -12560,7 +12573,7 @@
       <c r="Q6" s="124"/>
       <c r="R6" s="124"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -12584,7 +12597,7 @@
       <c r="Q7" s="124"/>
       <c r="R7" s="124"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -12608,7 +12621,7 @@
       <c r="Q8" s="124"/>
       <c r="R8" s="124"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -12632,7 +12645,7 @@
       <c r="Q9" s="124"/>
       <c r="R9" s="124"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
@@ -12660,11 +12673,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D12" s="4" t="s">
         <v>13</v>
       </c>
@@ -12682,7 +12695,7 @@
       <c r="Q12" s="124"/>
       <c r="R12" s="124"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -12732,7 +12745,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
         <v>39</v>
       </c>
@@ -12782,7 +12795,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>90</v>
       </c>
@@ -12809,7 +12822,7 @@
       <c r="Q15" s="126"/>
       <c r="R15" s="126"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f>L16</f>
         <v>FTE-COMCOA</v>
@@ -12854,7 +12867,7 @@
       <c r="Q16" s="124"/>
       <c r="R16" s="124"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-COMGAS</v>
@@ -12897,7 +12910,7 @@
       <c r="Q17" s="124"/>
       <c r="R17" s="124"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-COMOIL</v>
@@ -12943,7 +12956,7 @@
       <c r="Q18" s="124"/>
       <c r="R18" s="124"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C19" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -12977,7 +12990,7 @@
       <c r="Q19" s="124"/>
       <c r="R19" s="124"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -13011,7 +13024,7 @@
       <c r="Q20" s="124"/>
       <c r="R20" s="124"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -13047,7 +13060,7 @@
       <c r="Q21" s="124"/>
       <c r="R21" s="124"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -13061,7 +13074,7 @@
       <c r="H22" s="10"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -13075,7 +13088,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B24" t="str">
         <f>L19</f>
         <v>FTE-COMBIO</v>
@@ -13100,7 +13113,7 @@
       <c r="K24" s="23"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-COMSOL</v>
@@ -13125,7 +13138,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" s="5" t="str">
         <f>L21</f>
         <v>FTE-COMELC</v>
@@ -13152,7 +13165,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E27" s="11"/>
       <c r="F27" s="11"/>
       <c r="G27" s="66"/>
@@ -13161,20 +13174,20 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
       <c r="H28" s="10"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="11"/>
@@ -13182,7 +13195,7 @@
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="11"/>
@@ -13190,7 +13203,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="23"/>
       <c r="D32" s="23"/>
       <c r="E32" s="95"/>
@@ -13198,7 +13211,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -13206,7 +13219,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -13214,7 +13227,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="95"/>
@@ -13222,7 +13235,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="11"/>
@@ -13230,7 +13243,7 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="11"/>
@@ -13238,13 +13251,13 @@
       <c r="G37" s="66"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="39"/>
       <c r="C41" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="61"/>
       <c r="C42" s="1" t="s">
         <v>150</v>
@@ -13261,32 +13274,32 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:U35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
     <col min="10" max="10" width="2" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.85546875" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -13309,7 +13322,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B6</f>
         <v>COM</v>
@@ -13348,7 +13361,7 @@
       <c r="T2" s="120"/>
       <c r="U2" s="120"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M3" s="121" t="s">
         <v>7</v>
       </c>
@@ -13377,7 +13390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -13411,7 +13424,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -13438,7 +13451,7 @@
       <c r="T5" s="120"/>
       <c r="U5" s="120"/>
     </row>
-    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -13463,7 +13476,7 @@
       <c r="T6" s="120"/>
       <c r="U6" s="120"/>
     </row>
-    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -13488,7 +13501,7 @@
       <c r="T7" s="120"/>
       <c r="U7" s="120"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M8" s="124" t="s">
         <v>106</v>
       </c>
@@ -13510,7 +13523,7 @@
       <c r="T8" s="124"/>
       <c r="U8" s="124"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -13530,7 +13543,7 @@
       <c r="T10" s="124"/>
       <c r="U10" s="124"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -13587,7 +13600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -13644,7 +13657,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -13674,7 +13687,7 @@
       <c r="T13" s="123"/>
       <c r="U13" s="123"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
         <f>O14</f>
         <v>CSCESOL</v>
@@ -13730,7 +13743,7 @@
       <c r="T14" s="124"/>
       <c r="U14" s="124"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="str">
         <f t="shared" ref="B15:B18" si="2">O15</f>
         <v>CSCEELC</v>
@@ -13787,7 +13800,7 @@
       <c r="T15" s="124"/>
       <c r="U15" s="124"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" s="105" t="str">
         <f t="shared" si="2"/>
         <v>CAPEELC</v>
@@ -13845,7 +13858,7 @@
       <c r="T16" s="127"/>
       <c r="U16" s="127"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f t="shared" si="2"/>
         <v>COTEOIL</v>
@@ -13902,7 +13915,7 @@
       <c r="T17" s="124"/>
       <c r="U17" s="124"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f t="shared" si="2"/>
         <v>COTEELC</v>
@@ -13959,61 +13972,61 @@
       <c r="T18" s="124"/>
       <c r="U18" s="124"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E19" s="6"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E20" s="6"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="P20" s="19"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E21" s="6"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="P21" s="19"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E22" s="6"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="P22" s="19"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -14029,29 +14042,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:R38"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="7.109375" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.109375" customWidth="1"/>
-    <col min="15" max="15" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" customWidth="1"/>
+    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -14072,7 +14085,7 @@
       </c>
       <c r="H1" s="27"/>
     </row>
-    <row r="2" spans="2:18" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B5</f>
         <v>RSD</v>
@@ -14108,7 +14121,7 @@
       <c r="Q2" s="120"/>
       <c r="R2" s="120"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
       <c r="J3" s="121" t="s">
         <v>7</v>
       </c>
@@ -14137,7 +14150,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -14171,7 +14184,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
       <c r="G5" s="66"/>
@@ -14197,7 +14210,7 @@
       <c r="Q5" s="124"/>
       <c r="R5" s="124"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="66"/>
@@ -14221,7 +14234,7 @@
       <c r="Q6" s="124"/>
       <c r="R6" s="124"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="66"/>
@@ -14245,7 +14258,7 @@
       <c r="Q7" s="124"/>
       <c r="R7" s="124"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="66"/>
@@ -14269,7 +14282,7 @@
       <c r="Q8" s="124"/>
       <c r="R8" s="124"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E9" s="11"/>
       <c r="F9" s="11"/>
       <c r="G9" s="66"/>
@@ -14293,7 +14306,7 @@
       <c r="Q9" s="124"/>
       <c r="R9" s="124"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="66"/>
@@ -14321,18 +14334,18 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
       <c r="G11" s="66"/>
       <c r="H11" s="10"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="L12" s="23"/>
       <c r="M12" s="24"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D13" s="4" t="s">
         <v>13</v>
       </c>
@@ -14350,7 +14363,7 @@
       <c r="Q13" s="124"/>
       <c r="R13" s="124"/>
     </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B14" s="17" t="s">
         <v>1</v>
       </c>
@@ -14400,7 +14413,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
@@ -14450,7 +14463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>90</v>
       </c>
@@ -14477,7 +14490,7 @@
       <c r="Q16" s="126"/>
       <c r="R16" s="126"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>L17</f>
         <v>FTE-RSDCOA</v>
@@ -14522,7 +14535,7 @@
       <c r="Q17" s="124"/>
       <c r="R17" s="124"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f>L18</f>
         <v>FTE-RSDGAS</v>
@@ -14565,7 +14578,7 @@
       <c r="Q18" s="124"/>
       <c r="R18" s="124"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
         <f>L19</f>
         <v>FTE-RSDOIL</v>
@@ -14610,7 +14623,7 @@
       <c r="Q19" s="124"/>
       <c r="R19" s="124"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C20" t="str">
         <f>'EB1'!$H$2</f>
         <v>KER</v>
@@ -14644,7 +14657,7 @@
       <c r="Q20" s="124"/>
       <c r="R20" s="124"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C21" t="str">
         <f>'EB1'!$I$2</f>
         <v>LPG</v>
@@ -14678,7 +14691,7 @@
       <c r="Q21" s="124"/>
       <c r="R21" s="124"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C22" t="str">
         <f>'EB1'!$J$2</f>
         <v>GSL</v>
@@ -14714,7 +14727,7 @@
       <c r="Q22" s="124"/>
       <c r="R22" s="124"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C23" t="str">
         <f>'EB1'!$L$2</f>
         <v>HFO</v>
@@ -14728,7 +14741,7 @@
       <c r="H23" s="10"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C24" t="str">
         <f>'EB1'!$M$2</f>
         <v>OPP</v>
@@ -14742,7 +14755,7 @@
       <c r="H24" s="10"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B25" t="str">
         <f>L20</f>
         <v>FTE-RSDBIO</v>
@@ -14767,7 +14780,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B26" t="str">
         <f>L21</f>
         <v>FTE-RSDSOL</v>
@@ -14792,7 +14805,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B27" t="str">
         <f>L22</f>
         <v>FTE-RSDELC</v>
@@ -14819,7 +14832,7 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="66"/>
@@ -14828,20 +14841,20 @@
       <c r="K28" s="23"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="66"/>
       <c r="H29" s="10"/>
       <c r="M29" s="19"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="66"/>
       <c r="H30" s="10"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B31" s="39"/>
       <c r="C31" s="1" t="s">
         <v>149</v>
@@ -14852,7 +14865,7 @@
       <c r="G31" s="66"/>
       <c r="H31" s="10"/>
     </row>
-    <row r="32" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B32" s="61"/>
       <c r="C32" s="1" t="s">
         <v>150</v>
@@ -14863,7 +14876,7 @@
       <c r="G32" s="66"/>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="23"/>
       <c r="D33" s="23"/>
       <c r="E33" s="95"/>
@@ -14871,7 +14884,7 @@
       <c r="G33" s="66"/>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="23"/>
       <c r="D34" s="23"/>
       <c r="E34" s="95"/>
@@ -14879,7 +14892,7 @@
       <c r="G34" s="66"/>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="23"/>
       <c r="D35" s="23"/>
       <c r="E35" s="95"/>
@@ -14887,7 +14900,7 @@
       <c r="G35" s="66"/>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="23"/>
       <c r="D36" s="23"/>
       <c r="E36" s="95"/>
@@ -14895,7 +14908,7 @@
       <c r="G36" s="66"/>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="23"/>
       <c r="D37" s="23"/>
       <c r="E37" s="11"/>
@@ -14903,7 +14916,7 @@
       <c r="G37" s="66"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="23"/>
       <c r="D38" s="23"/>
       <c r="E38" s="11"/>
@@ -14922,32 +14935,32 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B1:U35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.140625" customWidth="1"/>
     <col min="10" max="10" width="2" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.109375" customWidth="1"/>
-    <col min="15" max="15" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="77.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" customWidth="1"/>
-    <col min="18" max="18" width="11.6640625" customWidth="1"/>
-    <col min="19" max="19" width="13.44140625" customWidth="1"/>
-    <col min="20" max="20" width="13.88671875" customWidth="1"/>
-    <col min="21" max="21" width="8.44140625" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="77.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" customWidth="1"/>
+    <col min="20" max="20" width="13.85546875" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:21" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -14970,7 +14983,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="str">
         <f>'EB1'!B5</f>
         <v>RSD</v>
@@ -15009,7 +15022,7 @@
       <c r="T2" s="120"/>
       <c r="U2" s="120"/>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M3" s="121" t="s">
         <v>7</v>
       </c>
@@ -15038,7 +15051,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="22.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:21" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -15072,7 +15085,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -15099,7 +15112,7 @@
       <c r="T5" s="120"/>
       <c r="U5" s="120"/>
     </row>
-    <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -15124,7 +15137,7 @@
       <c r="T6" s="120"/>
       <c r="U6" s="120"/>
     </row>
-    <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -15149,7 +15162,7 @@
       <c r="T7" s="120"/>
       <c r="U7" s="120"/>
     </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:21" x14ac:dyDescent="0.2">
       <c r="M8" s="124" t="s">
         <v>106</v>
       </c>
@@ -15171,7 +15184,7 @@
       <c r="T8" s="124"/>
       <c r="U8" s="124"/>
     </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:21" x14ac:dyDescent="0.2">
       <c r="D10" s="4" t="s">
         <v>13</v>
       </c>
@@ -15191,7 +15204,7 @@
       <c r="T10" s="124"/>
       <c r="U10" s="124"/>
     </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B11" s="17" t="s">
         <v>1</v>
       </c>
@@ -15248,7 +15261,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:21" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
@@ -15305,7 +15318,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="2:21" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>90</v>
       </c>
@@ -15335,7 +15348,7 @@
       <c r="T13" s="123"/>
       <c r="U13" s="123"/>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="str">
         <f t="shared" ref="B14:B18" si="0">O14</f>
         <v>RSCEELC</v>
@@ -15391,7 +15404,7 @@
       <c r="T14" s="124"/>
       <c r="U14" s="124"/>
     </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B15" s="105" t="str">
         <f t="shared" si="0"/>
         <v>RAPEELC</v>
@@ -15448,7 +15461,7 @@
       <c r="T15" s="127"/>
       <c r="U15" s="127"/>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>ROTEOIL</v>
@@ -15505,7 +15518,7 @@
       <c r="T16" s="124"/>
       <c r="U16" s="124"/>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>ROTEBIO</v>
@@ -15562,7 +15575,7 @@
       <c r="T17" s="124"/>
       <c r="U17" s="124"/>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>ROTEELC</v>
@@ -15619,67 +15632,67 @@
       <c r="T18" s="124"/>
       <c r="U18" s="124"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E19" s="6"/>
       <c r="F19" s="16"/>
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E20" s="6"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
       <c r="H20" s="16"/>
       <c r="P20" s="19"/>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E21" s="6"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16"/>
       <c r="H21" s="16"/>
       <c r="P21" s="19"/>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="E22" s="6"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
       <c r="P22" s="19"/>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
       <c r="G25" s="1"/>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
     </row>
-    <row r="33" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
     </row>
-    <row r="34" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
     </row>
-    <row r="35" spans="10:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="10:12" x14ac:dyDescent="0.2">
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -15695,20 +15708,20 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="B1:K32"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
         <v>73</v>
       </c>
@@ -15722,7 +15735,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>83</v>
       </c>
@@ -15733,7 +15746,7 @@
         <v>PJ</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -15744,7 +15757,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>80</v>
       </c>
@@ -15770,7 +15783,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" ht="22.5" x14ac:dyDescent="0.2">
       <c r="B7" s="15" t="s">
         <v>81</v>
       </c>
@@ -15792,7 +15805,7 @@
       <c r="I7" s="15"/>
       <c r="J7" s="15"/>
     </row>
-    <row r="8" spans="2:11" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>90</v>
       </c>
@@ -15809,7 +15822,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="25" t="s">
         <v>35</v>
       </c>
@@ -15838,7 +15851,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -15867,7 +15880,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
@@ -15896,7 +15909,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>35</v>
       </c>
@@ -15925,7 +15938,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>35</v>
       </c>
@@ -15954,7 +15967,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>35</v>
       </c>
@@ -15983,7 +15996,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>35</v>
       </c>
@@ -16012,7 +16025,7 @@
       </c>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="5"/>
       <c r="C16" s="26"/>
       <c r="D16" s="26"/>
@@ -16031,7 +16044,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17" s="5"/>
       <c r="C17" s="26"/>
       <c r="D17" s="26"/>
@@ -16050,7 +16063,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G18" s="1" t="s">
         <v>123</v>
       </c>
@@ -16065,7 +16078,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G19" s="1" t="s">
         <v>123</v>
       </c>
@@ -16080,7 +16093,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G20" s="26" t="s">
         <v>123</v>
       </c>
@@ -16095,7 +16108,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G21" s="1" t="s">
         <v>123</v>
       </c>
@@ -16110,7 +16123,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G22" s="1" t="s">
         <v>123</v>
       </c>
@@ -16125,7 +16138,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G23" s="1" t="s">
         <v>123</v>
       </c>
@@ -16140,7 +16153,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G24" s="26" t="s">
         <v>123</v>
       </c>
@@ -16155,7 +16168,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G25" s="1" t="s">
         <v>123</v>
       </c>
@@ -16170,7 +16183,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G26" s="1" t="s">
         <v>123</v>
       </c>
@@ -16185,7 +16198,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G27" s="1" t="s">
         <v>123</v>
       </c>
@@ -16200,7 +16213,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G28" s="26" t="s">
         <v>123</v>
       </c>
@@ -16215,7 +16228,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G29" s="1" t="s">
         <v>123</v>
       </c>
@@ -16230,7 +16243,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>149</v>
@@ -16249,7 +16262,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31" s="61"/>
       <c r="C31" s="1" t="s">
         <v>150</v>
@@ -16268,7 +16281,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G32" s="26" t="s">
         <v>123</v>
       </c>
